--- a/exports/SWIGGY_full_report.xlsx
+++ b/exports/SWIGGY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>20.05</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45660.55208333334</v>
+        <v>45663.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>541.5</v>
+        <v>527.7</v>
       </c>
       <c r="I2" t="n">
         <v>528.5874339926299</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K2" t="n">
-        <v>30.26</v>
+        <v>26.94</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.42</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45779.55208333334</v>
+        <v>45782.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>305.4</v>
+        <v>332.95</v>
       </c>
       <c r="I3" t="n">
         <v>330.276865373233</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>116.1666666666667</v>
+        <v>119</v>
       </c>
       <c r="K3" t="n">
-        <v>42.13</v>
+        <v>36.91</v>
       </c>
       <c r="L3" t="n">
         <v>3.57</v>
@@ -612,7 +647,7 @@
         <v>3.38</v>
       </c>
       <c r="N3" t="n">
-        <v>8.15</v>
+        <v>12.3</v>
       </c>
       <c r="O3" t="n">
         <v>-0.28</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.69</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45873.55208333334</v>
+        <v>45874.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>398.5</v>
+        <v>389.45</v>
       </c>
       <c r="I4" t="n">
         <v>390.4570782443606</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>91.16666666666667</v>
+        <v>92</v>
       </c>
       <c r="K4" t="n">
-        <v>19.69</v>
+        <v>16.97</v>
       </c>
       <c r="L4" t="n">
         <v>10.8</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.35</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>407.65</v>
+        <v>419.95</v>
       </c>
       <c r="I5" t="n">
         <v>418.3103934851794</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.67</v>
+        <v>-7.83</v>
       </c>
       <c r="L5" t="n">
-        <v>5.49</v>
+        <v>8.41</v>
       </c>
       <c r="M5" t="n">
         <v>2.73</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>438.5</v>
+        <v>429</v>
       </c>
       <c r="I6" t="n">
         <v>431.1156522068774</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
-        <v>4.42</v>
+        <v>2.16</v>
       </c>
       <c r="L6" t="n">
         <v>3.29</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.5</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45944.38541666666</v>
+        <v>45944.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>437</v>
+        <v>438.1</v>
       </c>
       <c r="I7" t="n">
         <v>437.6483389592926</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.86</v>
+        <v>-2.12</v>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>4.36</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>448</v>
+        <v>426.4</v>
       </c>
       <c r="I8" t="n">
         <v>428.6490997385509</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>2.26</v>
+        <v>-2.67</v>
       </c>
       <c r="L8" t="n">
-        <v>0.55</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01</v>
+        <v>0.22</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O8" t="n">
         <v>0.83</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.1</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45993.55208333334</v>
+        <v>45994.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>397.5</v>
+        <v>402.8</v>
       </c>
       <c r="I9" t="n">
         <v>401.4819856130783</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K9" t="n">
-        <v>6.78</v>
+        <v>5.53</v>
       </c>
       <c r="L9" t="n">
         <v>4.83</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.65</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>395.95</v>
+        <v>388</v>
       </c>
       <c r="I10" t="n">
         <v>389.1880075212708</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7</v>
+        <v>-3.67</v>
       </c>
       <c r="L10" t="n">
         <v>5.62</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.34</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46062.55208333334</v>
+        <v>46063.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>334.8</v>
+        <v>350.1</v>
       </c>
       <c r="I11" t="n">
         <v>338.840815522248</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K11" t="n">
-        <v>13.71</v>
+        <v>9.77</v>
       </c>
       <c r="L11" t="n">
         <v>3.02</v>
@@ -1068,7 +1199,7 @@
         <v>3.32</v>
       </c>
       <c r="N11" t="n">
-        <v>4.82</v>
+        <v>5.85</v>
       </c>
       <c r="O11" t="n">
         <v>0.14</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>10.6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46072.55208333334</v>
+        <v>46073.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>326.2</v>
+        <v>323.4</v>
       </c>
       <c r="I12" t="n">
         <v>324.4829413130053</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.83</v>
+        <v>-7.63</v>
       </c>
       <c r="L12" t="n">
-        <v>7.17</v>
+        <v>7.93</v>
       </c>
       <c r="M12" t="n">
         <v>0.83</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.76</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46133.55208333334</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>284.4</v>
+        <v>291.25</v>
       </c>
       <c r="I13" t="n">
         <v>285.9695103598037</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K13" t="n">
-        <v>12.06</v>
+        <v>9.94</v>
       </c>
       <c r="L13" t="n">
         <v>1.64</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>8.66</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46140.55208333334</v>
+        <v>46141.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>289.9</v>
+        <v>274.35</v>
       </c>
       <c r="I14" t="n">
         <v>274.6840812403173</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.46</v>
+        <v>-5.8</v>
       </c>
       <c r="L14" t="n">
-        <v>4.67</v>
+        <v>6.44</v>
       </c>
       <c r="M14" t="n">
         <v>0.87</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>5.21</v>
       </c>
       <c r="O14" t="n">
         <v>3.55</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.81</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46168.55208333334</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>255</v>
+        <v>269.1</v>
       </c>
       <c r="I15" t="n">
         <v>265.8851248334078</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>7.05</v>
+        <v>1.91</v>
       </c>
       <c r="L15" t="n">
         <v>5.19</v>
@@ -1296,7 +1475,7 @@
         <v>1.25</v>
       </c>
       <c r="N15" t="n">
-        <v>2.69</v>
+        <v>6.49</v>
       </c>
       <c r="O15" t="n">
         <v>-5.21</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>9.52</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46174.38541666666</v>
+        <v>46174.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>254.1</v>
+        <v>249.5</v>
       </c>
       <c r="I16" t="n">
         <v>252.1649770968012</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.57</v>
+        <v>-7.28</v>
       </c>
       <c r="L16" t="n">
-        <v>6.63</v>
+        <v>7.56</v>
       </c>
       <c r="M16" t="n">
         <v>0.33</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>8.9</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>250.1</v>
+        <v>261.75</v>
       </c>
       <c r="I17" t="n">
         <v>258.4466122196779</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.24</v>
+        <v>-4.91</v>
       </c>
       <c r="L17" t="n">
-        <v>3.35</v>
+        <v>7.07</v>
       </c>
       <c r="M17" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="N17" t="n">
         <v>4.12</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>8.9</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46196.55208333334</v>
+        <v>46197.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>249.15</v>
+        <v>242.95</v>
       </c>
       <c r="I18" t="n">
         <v>243.6816338723259</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.81</v>
+        <v>-7.18</v>
       </c>
       <c r="L18" t="n">
-        <v>4.87</v>
+        <v>8.42</v>
       </c>
       <c r="M18" t="n">
         <v>0.18</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>7.95</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>250</v>
+        <v>263.05</v>
       </c>
       <c r="I19" t="n">
         <v>253.5082088038048</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.9</v>
+        <v>-8.27</v>
       </c>
       <c r="L19" t="n">
-        <v>4.73</v>
+        <v>8.75</v>
       </c>
       <c r="M19" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>2.97</v>
+        <v>6.49</v>
       </c>
       <c r="O19" t="n">
         <v>-1.71</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>8.84</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46226.55208333334</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>261.29</v>
+        <v>249.38</v>
       </c>
       <c r="I20" t="n">
         <v>255.7015522668176</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.67</v>
+        <v>-5.2</v>
       </c>
       <c r="L20" t="n">
-        <v>4.96</v>
+        <v>7.81</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
         <v>6.49</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>9.69</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>270.25</v>
+        <v>288</v>
       </c>
       <c r="I21" t="n">
         <v>272.432021280662</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.369999999999999</v>
+        <v>-15.49</v>
       </c>
       <c r="L21" t="n">
-        <v>9.470000000000001</v>
+        <v>16.28</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>4.83</v>
+        <v>6.01</v>
       </c>
       <c r="O21" t="n">
         <v>-3.75</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>12.06</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>276</v>
+        <v>267.3</v>
       </c>
       <c r="I22" t="n">
         <v>274.3213036134132</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.17</v>
+        <v>-7.19</v>
       </c>
       <c r="L22" t="n">
-        <v>6.34</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>1.29</v>
+        <v>2.17</v>
       </c>
       <c r="N22" t="n">
         <v>3.07</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>5.74</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46274.38541666666</v>
+        <v>46274.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>280.2</v>
+        <v>283.2</v>
       </c>
       <c r="I23" t="n">
         <v>282.4071344423277</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.83</v>
+        <v>-5.95</v>
       </c>
       <c r="L23" t="n">
-        <v>6.4</v>
+        <v>6.83</v>
       </c>
       <c r="M23" t="n">
         <v>0.11</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>6.57</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46289.55208333334</v>
+        <v>46290.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>267.6</v>
+        <v>261.8</v>
       </c>
       <c r="I24" t="n">
         <v>265.6620439253719</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.51</v>
+        <v>-7.56</v>
       </c>
       <c r="L24" t="n">
-        <v>6.21</v>
+        <v>7.7</v>
       </c>
       <c r="M24" t="n">
         <v>1.15</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1869,6 +2168,14 @@
       <c r="Q25" t="n">
         <v>42</v>
       </c>
+      <c r="R25" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2815,7 +3122,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.2</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="6">
@@ -2825,7 +3132,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -2835,7 +3142,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>116.2</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8">
@@ -2845,7 +3152,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -2855,7 +3162,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -2865,7 +3172,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57.4</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="11">
@@ -2905,7 +3212,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.73</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="15">
@@ -2915,7 +3222,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.24</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="16">
@@ -2925,7 +3232,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.35</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="17">
@@ -2935,7 +3242,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42.13</v>
+        <v>36.91</v>
       </c>
     </row>
     <row r="18">
@@ -2945,7 +3252,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39.1</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="19">
@@ -2955,7 +3262,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.91</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="20">
@@ -2965,7 +3272,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.87</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="21">
@@ -2975,7 +3282,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.8</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="22">
@@ -2985,7 +3292,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -2995,7 +3302,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -3005,7 +3312,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="25">
@@ -3025,7 +3332,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.86</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="27">
@@ -3035,7 +3342,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.15</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="28">
@@ -3045,7 +3352,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
